--- a/data/opponent_priors.xlsx
+++ b/data/opponent_priors.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="3">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -865,7 +865,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>D_agm</t>
+          <t>D_resign_late</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -893,7 +893,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D_disgrace</t>
+          <t>D_negotiate</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>D_adverse_review</t>
+          <t>D_agm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="E18" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" t="n">
         <v>10</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>D_disgrace</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>W_resign</t>
+          <t>D_adverse_review</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>W_stay_sacked</t>
+          <t>gamma</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>W_stay_kept</t>
+          <t>W_resign</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>D_resign</t>
+          <t>W_stay_sacked</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D_sacked</t>
+          <t>W_stay_kept</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D_agm</t>
+          <t>D_resign</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D_disgrace</t>
+          <t>D_sacked</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="E26" t="n">
+        <v>100</v>
+      </c>
+      <c r="F26" t="n">
         <v>30</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1173,19 +1173,887 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>D_resign_late</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>D_negotiate</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>45</v>
+      </c>
+      <c r="F28" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D_agm</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>D_disgrace</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>D_adverse_review</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>10</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F31" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>vote_penalty_weight</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ceo_loss_cost</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>spill_risk_weight</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>review_car_weight</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>15</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>review_direct_cost_weight</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>implementation_cost_sack</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>early_ceo_departure_cost</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>D_stay</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>D_stay</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>25</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>loss_aversion</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>W_ref</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>loss_aversion</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>W_ref</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>loss_aversion_D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>loss_aversion_D</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>second_strike_spill_penalty</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>board_regulatory_liability</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>board_d1_liability</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>qantas_legal_d1_penalty</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>qantas_legal_d_rev_penalty</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>adverse_review_ceo_present_penalty</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>second_strike_spill_penalty</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>8</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>board_regulatory_liability</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>board_d1_liability</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>qantas_legal_d1_penalty</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>qantas_legal_d_rev_penalty</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>adverse_review_ceo_present_penalty</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/opponent_priors.xlsx
+++ b/data/opponent_priors.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2056,6 +2056,174 @@
         <v>2</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_strike</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_overwhelming</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_adverse</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_strike</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_overwhelming</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_adverse</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/opponent_priors.xlsx
+++ b/data/opponent_priors.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>early_ceo_departure_cost</t>
+          <t>board_passivity_after_departure</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>adverse_review_ceo_present_penalty</t>
+          <t>negative_review_finding_penalty</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>second_strike_spill_penalty</t>
+          <t>balanced_review_finding_penalty</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>board_regulatory_liability</t>
+          <t>second_strike_spill_penalty</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>board_d1_liability</t>
+          <t>board_regulatory_liability</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="56">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>qantas_legal_d1_penalty</t>
+          <t>board_d1_liability</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>qantas_legal_d_rev_penalty</t>
+          <t>qantas_legal_d1_penalty</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>adverse_review_ceo_present_penalty</t>
+          <t>qantas_legal_d_rev_penalty</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2069,25 +2069,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_strike</t>
+          <t>negative_review_finding_penalty</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>lognormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-0.92</v>
+        <v>5</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2097,19 +2097,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_overwhelming</t>
+          <t>balanced_review_finding_penalty</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>lognormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-0.6899999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_adverse</t>
+          <t>ceo_loss_shock_strike</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="F61" t="n">
         <v>0.4</v>
@@ -2143,7 +2143,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_strike</t>
+          <t>ceo_loss_shock_overwhelming</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>-0.92</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F62" t="n">
         <v>0.4</v>
@@ -2171,7 +2171,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_overwhelming</t>
+          <t>ceo_loss_shock_adverse</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2209,18 +2209,74 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>ceo_loss_shock_strike</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ceo_loss_shock_overwhelming</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>lognormal</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>ceo_loss_shock_adverse</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>lognormal</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E66" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F66" t="n">
         <v>0.4</v>
       </c>
     </row>

--- a/data/opponent_priors.xlsx
+++ b/data/opponent_priors.xlsx
@@ -425,36 +425,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>perspective_actor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>target_actor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>parameter_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>param1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>param2</t>
         </is>
@@ -463,45 +463,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mobilisation_cost</t>
+          <t>vote_penalty_weight</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lognormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-1.2</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vote_reward_weight</t>
+          <t>ceo_loss_cost</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="n">
         <v>0.5</v>
@@ -519,45 +519,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ceo_removal_reward</t>
+          <t>implementation_cost_review</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lognormal</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>-1.2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reputational_gain_weight</t>
+          <t>spill_risk_weight</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F5" t="n">
         <v>0.5</v>
@@ -575,17 +575,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vote_penalty_weight</t>
+          <t>gamma</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
         <v>0.5</v>
@@ -603,17 +603,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ceo_loss_cost</t>
+          <t>W_resign</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,35 +622,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>implementation_cost_review</t>
+          <t>W_stay_sacked</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lognormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-1.2</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
         <v>0.3</v>
@@ -659,17 +659,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spill_risk_weight</t>
+          <t>W_stay_kept</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -697,7 +697,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>D_resign</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -725,7 +725,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>W_resign</t>
+          <t>D_sacked</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -753,7 +753,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>W_stay_sacked</t>
+          <t>D_resign_late</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -781,7 +781,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>W_stay_kept</t>
+          <t>D_negotiate</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -809,7 +809,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>D_resign</t>
+          <t>D_agm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -837,7 +837,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D_sacked</t>
+          <t>D_disgrace</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -865,7 +865,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>D_resign_late</t>
+          <t>D_adverse_review</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -874,16 +874,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D_negotiate</t>
+          <t>gamma</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>1.5</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>D_agm</t>
+          <t>W_resign</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D_disgrace</t>
+          <t>W_stay_sacked</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D_adverse_review</t>
+          <t>W_stay_kept</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gamma</t>
+          <t>D_resign</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>W_resign</t>
+          <t>D_sacked</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>W_stay_sacked</t>
+          <t>D_resign_late</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5</v>
+        <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>W_stay_kept</t>
+          <t>D_negotiate</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D_resign</t>
+          <t>D_agm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D_sacked</t>
+          <t>D_disgrace</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D_resign_late</t>
+          <t>D_adverse_review</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1182,26 +1182,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>D_negotiate</t>
+          <t>vote_penalty_weight</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1210,26 +1210,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D_agm</t>
+          <t>ceo_loss_cost</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1238,26 +1238,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>1.5</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D_disgrace</t>
+          <t>spill_risk_weight</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1266,26 +1266,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>2.5</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>D_adverse_review</t>
+          <t>review_car_weight</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>vote_penalty_weight</t>
+          <t>review_direct_cost_weight</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ceo_loss_cost</t>
+          <t>implementation_cost_sack</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>spill_risk_weight</t>
+          <t>board_passivity_after_departure</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1378,26 +1378,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>review_car_weight</t>
+          <t>D_stay</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1406,26 +1406,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>review_direct_cost_weight</t>
+          <t>D_stay</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1434,26 +1434,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>implementation_cost_sack</t>
+          <t>loss_aversion</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1462,26 +1462,26 @@
         </is>
       </c>
       <c r="E37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F37" t="n">
         <v>0.3</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>board_passivity_after_departure</t>
+          <t>W_ref</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D_stay</t>
+          <t>loss_aversion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>25</v>
+        <v>2.25</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="40">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D_stay</t>
+          <t>W_ref</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>loss_aversion</t>
+          <t>loss_aversion_D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>W_ref</t>
+          <t>loss_aversion_D</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>16</v>
+        <v>2.25</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="43">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>loss_aversion</t>
+          <t>second_strike_spill_penalty</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.25</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>W_ref</t>
+          <t>board_regulatory_liability</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1658,26 +1658,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>loss_aversion_D</t>
+          <t>board_d1_liability</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>loss_aversion_D</t>
+          <t>qantas_legal_d1_penalty</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>second_strike_spill_penalty</t>
+          <t>qantas_legal_d_rev_penalty</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="48">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>board_regulatory_liability</t>
+          <t>negative_review_finding_penalty</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>board_d1_liability</t>
+          <t>balanced_review_finding_penalty</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1798,16 +1798,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>qantas_legal_d1_penalty</t>
+          <t>second_strike_spill_penalty</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>qantas_legal_d_rev_penalty</t>
+          <t>board_regulatory_liability</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1854,16 +1854,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>negative_review_finding_penalty</t>
+          <t>board_d1_liability</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1882,16 +1882,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>balanced_review_finding_penalty</t>
+          <t>qantas_legal_d1_penalty</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>second_strike_spill_penalty</t>
+          <t>qantas_legal_d_rev_penalty</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="55">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>board_regulatory_liability</t>
+          <t>negative_review_finding_penalty</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1969,7 +1969,7 @@
         <v>5</v>
       </c>
       <c r="F55" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>board_d1_liability</t>
+          <t>balanced_review_finding_penalty</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1994,16 +1994,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2013,25 +2013,25 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>qantas_legal_d1_penalty</t>
+          <t>ceo_loss_shock_strike</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lognormal</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>-0.92</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2041,25 +2041,25 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>qantas_legal_d_rev_penalty</t>
+          <t>ceo_loss_shock_overwhelming</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lognormal</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2069,19 +2069,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>negative_review_finding_penalty</t>
+          <t>ceo_loss_shock_adverse</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lognormal</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="60">
@@ -2097,25 +2097,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>balanced_review_finding_penalty</t>
+          <t>ceo_loss_shock_strike</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lognormal</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.5</v>
+        <v>-0.92</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_strike</t>
+          <t>ceo_loss_shock_overwhelming</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>-0.92</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F61" t="n">
         <v>0.4</v>
@@ -2143,7 +2143,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_overwhelming</t>
+          <t>ceo_loss_shock_adverse</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2171,54 +2171,54 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASA</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_adverse</t>
+          <t>strike_ba_shift</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>lognormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>-0.6899999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_strike</t>
+          <t>strike_ol_shift</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>lognormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>-0.92</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
         <v>0.4</v>
@@ -2227,26 +2227,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_overwhelming</t>
+          <t>overwhelming_ba_shift</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>lognormal</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0.4</v>
@@ -2255,29 +2255,253 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Board</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Board</t>
+          <t>ASA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ceo_loss_shock_adverse</t>
+          <t>overwhelming_ol_shift</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ceo_removal_ba_shift</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ceo_removal_fw_shift</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>negative_review_td_shift</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>negative_review_egr_shift</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>balanced_review_td_shift</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>market_alignment_ol_shift</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>market_alignment_pf_shift</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>mobilisation_cost</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>lognormal</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.4</v>
+      <c r="E74" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
